--- a/Ontologia de Solos/Pesquisa SCOPUS/Questões de Competência para o Multisoils.xlsx
+++ b/Ontologia de Solos/Pesquisa SCOPUS/Questões de Competência para o Multisoils.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\artigos\Ontologia de Solos\Pesquisa SCOPUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0B834AA-E57C-4675-945B-CAD9B758298B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9870362-D265-4C85-A469-98CE64E5B39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{16828531-F49B-4221-9F2E-E86F20E19D5F}"/>
   </bookViews>
@@ -1282,6 +1282,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B228FE48-8214-4A41-9C85-2F59921A0ADC}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="38.77734375" defaultRowHeight="14.4"/>
   <cols>
@@ -1432,5 +1435,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" scale="58" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>